--- a/docs/reports/2026-08-16-결함별-성능비교.xlsx
+++ b/docs/reports/2026-08-16-결함별-성능비교.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,8 +32,16 @@
       <sz val="13"/>
     </font>
     <font>
+      <sz val="9"/>
+    </font>
+    <font>
       <i val="1"/>
       <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00C00000"/>
       <sz val="9"/>
     </font>
     <font>
@@ -44,15 +52,35 @@
       <b val="1"/>
     </font>
     <font>
-      <color rgb="00999999"/>
+      <color rgb="00595959"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -72,30 +100,49 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -463,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -473,7 +520,7 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -486,1108 +533,1160 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>굵은 글씨 = 공통 검증셋(common_holdout, 두 모델 학습분 모두 제외)으로 직접 비교한 12종 · 회색 = 이 판으로 측정 불가, 기존 판 참고치</t>
+          <t>■ 초록</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>common_holdout — 두 모델 학습분을 모두 제외한 공통 검증셋. 이 색끼리만 직접 비교할 수 있다 (결함 12종 × 30장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>■ 노랑</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>testset_bycode — S20/AIHub 도메인, 종류당 20장. 필터C 참고치</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>■ 주황</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>test3_holdout — 야장(실제 조사영상) 80%. test3 참고치</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>■ 회색</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>측정 불가 — 두 모델이 원본을 전량 학습에 써서 검증할 사진이 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>※ 색이 다른 칸은 서로 다른 사진에서 잰 값이다 — 나란히 있어도 비교가 아니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>결함코드</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>장수</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>CLS 탐지율</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>CLS 이름정확도</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>DET 탐지율</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>DET 이름정확도</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>합집합</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>CC</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B9" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C9" s="10" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D9" s="10" t="n">
         <v>0.2666666666666667</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E9" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F9" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G9" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B10" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C10" s="10" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D10" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E10" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F10" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G10" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>CM</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="n">
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="n">
         <v>0.6</v>
       </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="n">
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>참고치 · 야장 20장</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>CLS: testset_bycode 20장 · DET: 야장 20장</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B12" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C12" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D12" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E12" s="10" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F12" s="10" t="n">
         <v>0.8666666666666667</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G12" s="10" t="n">
         <v>0.8666666666666667</v>
       </c>
-      <c r="H8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>BC</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B13" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C13" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D13" s="10" t="n">
         <v>0.8666666666666667</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E13" s="10" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F13" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G13" s="10" t="n">
         <v>0.8666666666666667</v>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>YOLO 미학습(구조적 0%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>YOLO에 클래스 없음 → DET 0%는 구조적</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>LD</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B14" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C14" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D14" s="10" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E14" s="10" t="n">
         <v>0.7333333333333333</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F14" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G14" s="10" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>YOLO 미학습(구조적 0%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>YOLO에 클래스 없음 → DET 0%는 구조적</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>DF</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B15" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C15" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D15" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E15" s="10" t="n">
         <v>0.6333333333333333</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F15" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="G15" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>YOLO 미학습(구조적 0%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>YOLO에 클래스 없음 → DET 0%는 구조적</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>BK</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B16" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C16" s="10" t="n">
         <v>0.7666666666666667</v>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="D16" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E16" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F16" s="10" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="G16" s="10" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="H12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>CX</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>참고치 · 데이터 없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>양쪽 데이터 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>PO</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="n">
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="n">
         <v>0.3</v>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="n">
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>참고치 · 야장 20장</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>CLS: testset_bycode 20장 · DET: 야장 20장</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>HL</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="n">
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="n">
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>참고치 · 야장 3장</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>CLS: testset_bycode 20장 · DET: 야장 3장 · DET 표본 3장뿐</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B20" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C20" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="D16" s="5" t="n">
+      <c r="D20" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="E20" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="F20" s="10" t="n">
         <v>0.9666666666666667</v>
       </c>
-      <c r="G16" s="5" t="n">
+      <c r="G20" s="10" t="n">
         <v>0.9666666666666667</v>
       </c>
-      <c r="H16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>LS</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="n">
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="n">
         <v>0.45</v>
       </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="n">
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="n">
         <v>0.3</v>
       </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>참고치 · 야장 20장</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>CLS: testset_bycode 20장 · DET: 야장 20장</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>JS</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="n">
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="n">
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>참고치 · 야장 20장</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>CLS: testset_bycode 20장 · DET: 야장 20장</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>JF</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B23" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C23" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="D19" s="5" t="n">
+      <c r="D23" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="E19" s="5" t="n">
+      <c r="E23" s="10" t="n">
         <v>0.9666666666666667</v>
       </c>
-      <c r="F19" s="5" t="n">
+      <c r="F23" s="10" t="n">
         <v>0.8666666666666667</v>
       </c>
-      <c r="G19" s="5" t="n">
+      <c r="G23" s="10" t="n">
         <v>0.8666666666666667</v>
       </c>
-      <c r="H19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>JD</t>
         </is>
       </c>
-      <c r="B20" s="4" t="n">
+      <c r="B24" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="C20" s="5" t="n">
+      <c r="C24" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="D20" s="5" t="n">
+      <c r="D24" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="E20" s="5" t="n">
+      <c r="E24" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="5" t="n">
+      <c r="F24" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="5" t="n">
+      <c r="G24" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>NS</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>참고치 · 데이터 없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>양쪽 데이터 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="n">
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="n">
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>참고치 · 야장 10장</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>CLS: testset_bycode 20장 · DET: 야장 10장 · DET 표본 10장</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="n">
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="n">
         <v>0.93</v>
       </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>참고치 · YOLO 미학습</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>CLS: testset_bycode 15장 · YOLO 미학습</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>DS</t>
         </is>
       </c>
-      <c r="B24" s="4" t="n">
+      <c r="B28" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="C24" s="5" t="n">
+      <c r="C28" s="10" t="n">
         <v>0.7333333333333333</v>
       </c>
-      <c r="D24" s="5" t="n">
+      <c r="D28" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="E24" s="5" t="n">
+      <c r="E28" s="10" t="n">
         <v>0.9666666666666667</v>
       </c>
-      <c r="F24" s="5" t="n">
+      <c r="F28" s="10" t="n">
         <v>0.9666666666666667</v>
       </c>
-      <c r="G24" s="5" t="n">
+      <c r="G28" s="10" t="n">
         <v>0.9666666666666667</v>
       </c>
-      <c r="H24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>DG</t>
         </is>
       </c>
-      <c r="B25" s="4" t="n">
+      <c r="B29" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C29" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="5" t="n">
+      <c r="D29" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E25" s="5" t="n">
+      <c r="E29" s="10" t="n">
         <v>0.5333333333333333</v>
       </c>
-      <c r="F25" s="5" t="n">
+      <c r="F29" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="5" t="n">
+      <c r="G29" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>YOLO 미학습(구조적 0%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>YOLO에 클래스 없음 → DET 0%는 구조적</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>TO</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="n">
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="n">
         <v>0.75</v>
       </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="n">
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="n">
         <v>0.8</v>
       </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>참고치 · 야장 20장</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>CLS: testset_bycode 20장 · DET: 야장 20장</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>RT</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="n">
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="n">
         <v>0.65</v>
       </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="n">
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>참고치 · 야장 19장</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>CLS: testset_bycode 20장 · DET: 야장 19장</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>IF</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="n">
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>참고치 · YOLO 미학습</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>CLS: testset_bycode 20장 · YOLO 미학습</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>PB</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>참고치 · 데이터 없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>양쪽 데이터 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>ETC</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="n">
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>참고치 · 기타(결함 종류 아님)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>CLS: testset_bycode 20장 · 기타(결함 종류 아님)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>[측정한 12종 전체 평균] — 이 판의 대표값</t>
         </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>CLS 탐지율</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="n">
-        <v>0.9055555555555556</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>CLS 이름정확도</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="n">
-        <v>0.4083333333333333</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>DET 탐지율</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="n">
-        <v>0.8833333333333333</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>DET 이름정확도</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="n">
-        <v>0.6166666666666667</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>합집합(둘 중 하나라도 맞힘)</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="n">
-        <v>0.9027777777777778</v>
+          <t>CLS 탐지율</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="n">
+        <v>0.9055555555555556</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>겹침(둘 다 맞힘)</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="n">
-        <v>0.1222222222222222</v>
+          <t>CLS 이름정확도</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="n">
+        <v>0.4083333333333333</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CLS만 맞힘</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="n">
-        <v>0.2861111111111111</v>
+          <t>DET 탐지율</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="n">
+        <v>0.8833333333333333</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DET만 맞힘</t>
-        </is>
-      </c>
-      <c r="B40" s="10" t="n">
-        <v>0.4944444444444445</v>
+          <t>DET 이름정확도</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="n">
+        <v>0.6166666666666667</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>합집합(둘 중 하나라도 맞힘)</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="n">
+        <v>0.9027777777777778</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="inlineStr">
-        <is>
-          <t>[둘 다 아는 8종만] — 같은 종류 맞대결</t>
-        </is>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>겹침(둘 다 맞힘)</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="n">
+        <v>0.1222222222222222</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CLS 탐지율</t>
-        </is>
-      </c>
-      <c r="B43" s="10" t="n">
-        <v>0.8583333333333333</v>
+          <t>CLS만 맞힘</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="n">
+        <v>0.2861111111111111</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CLS 이름정확도</t>
-        </is>
-      </c>
-      <c r="B44" s="10" t="n">
-        <v>0.1833333333333333</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>DET 탐지율</t>
-        </is>
-      </c>
-      <c r="B45" s="10" t="n">
-        <v>0.9833333333333333</v>
+          <t>DET만 맞힘</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="n">
+        <v>0.4944444444444445</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>DET 이름정확도</t>
-        </is>
-      </c>
-      <c r="B46" s="10" t="n">
-        <v>0.925</v>
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>[둘 다 아는 8종만] — 같은 종류 맞대결</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>합집합(둘 중 하나라도 맞힘)</t>
-        </is>
-      </c>
-      <c r="B47" s="10" t="n">
-        <v>0.925</v>
+          <t>CLS 탐지율</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="n">
+        <v>0.8583333333333333</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>겹침(둘 다 맞힘)</t>
-        </is>
-      </c>
-      <c r="B48" s="10" t="n">
+          <t>CLS 이름정확도</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="n">
         <v>0.1833333333333333</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CLS만 맞힘</t>
-        </is>
-      </c>
-      <c r="B49" s="10" t="n">
-        <v>0</v>
+          <t>DET 탐지율</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="n">
+        <v>0.9833333333333333</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>DET 이름정확도</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="n">
+        <v>0.925</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>합집합(둘 중 하나라도 맞힘)</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="n">
+        <v>0.925</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>겹침(둘 다 맞힘)</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="n">
+        <v>0.1833333333333333</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>CLS만 맞힘</t>
+        </is>
+      </c>
+      <c r="B53" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>DET만 맞힘</t>
         </is>
       </c>
-      <c r="B50" s="10" t="n">
+      <c r="B54" s="17" t="n">
         <v>0.7416666666666667</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
+  <mergeCells count="6">
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B2:H2"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="A6:H6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/reports/2026-08-16-결함별-성능비교.xlsx
+++ b/docs/reports/2026-08-16-결함별-성능비교.xlsx
@@ -100,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -129,13 +129,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -143,6 +143,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -510,17 +513,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -603,25 +607,30 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
+          <t>DET 탐지율</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>탐지 합집합</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
           <t>CLS 이름정확도</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>DET 탐지율</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>DET 이름정확도</t>
         </is>
       </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>합집합</t>
-        </is>
-      </c>
       <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>이름 합집합</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -640,18 +649,23 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="D9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="n">
         <v>0.2666666666666667</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>0.9</v>
       </c>
       <c r="G9" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
+      <c r="H9" s="10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
@@ -666,18 +680,23 @@
         <v>0.9333333333333333</v>
       </c>
       <c r="D10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="n">
         <v>0.2</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="10" t="n">
-        <v>0.9</v>
       </c>
       <c r="G10" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
+      <c r="H10" s="10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
@@ -690,28 +709,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C11" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="D11" s="13" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="n">
         <v>0.6</v>
       </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="14" t="n">
+      <c r="G11" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>CLS: testset_bycode 20장 · DET: 야장 20장</t>
         </is>
@@ -730,18 +750,23 @@
         <v>0.9</v>
       </c>
       <c r="D12" s="10" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="n">
         <v>0.1</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>0.9333333333333333</v>
-      </c>
-      <c r="F12" s="10" t="n">
-        <v>0.8666666666666667</v>
       </c>
       <c r="G12" s="10" t="n">
         <v>0.8666666666666667</v>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
+      <c r="H12" s="10" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="I12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
@@ -756,20 +781,25 @@
         <v>1</v>
       </c>
       <c r="D13" s="10" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="n">
         <v>0.8666666666666667</v>
       </c>
-      <c r="E13" s="10" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="F13" s="10" t="n">
+      <c r="G13" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="10" t="n">
+      <c r="H13" s="10" t="n">
         <v>0.8666666666666667</v>
       </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>YOLO에 클래스 없음 → DET 0%는 구조적</t>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>YOLO에 클래스 없음 → DET 이름 0%는 구조적</t>
         </is>
       </c>
     </row>
@@ -786,20 +816,25 @@
         <v>1</v>
       </c>
       <c r="D14" s="10" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="E14" s="10" t="n">
-        <v>0.7333333333333333</v>
-      </c>
-      <c r="F14" s="10" t="n">
+      <c r="G14" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="10" t="n">
+      <c r="H14" s="10" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>YOLO에 클래스 없음 → DET 0%는 구조적</t>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>YOLO에 클래스 없음 → DET 이름 0%는 구조적</t>
         </is>
       </c>
     </row>
@@ -816,20 +851,25 @@
         <v>1</v>
       </c>
       <c r="D15" s="10" t="n">
+        <v>0.6333333333333333</v>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="E15" s="10" t="n">
-        <v>0.6333333333333333</v>
-      </c>
-      <c r="F15" s="10" t="n">
+      <c r="G15" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="10" t="n">
+      <c r="H15" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>YOLO에 클래스 없음 → DET 0%는 구조적</t>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>YOLO에 클래스 없음 → DET 이름 0%는 구조적</t>
         </is>
       </c>
     </row>
@@ -846,18 +886,23 @@
         <v>0.7666666666666667</v>
       </c>
       <c r="D16" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="n">
         <v>0</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="10" t="n">
-        <v>0.9333333333333333</v>
       </c>
       <c r="G16" s="10" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="H16" s="3" t="inlineStr"/>
+      <c r="H16" s="10" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
@@ -870,7 +915,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -880,7 +925,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -890,12 +935,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>양쪽 데이터 없음</t>
         </is>
@@ -912,28 +962,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C18" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="D18" s="13" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="n">
         <v>0.3</v>
       </c>
-      <c r="E18" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F18" s="14" t="n">
+      <c r="G18" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H18" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>CLS: testset_bycode 20장 · DET: 야장 20장</t>
         </is>
@@ -950,28 +1001,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C19" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="D19" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F19" s="14" t="n">
+      <c r="G19" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H19" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>CLS: testset_bycode 20장 · DET: 야장 3장 · DET 표본 3장뿐</t>
         </is>
@@ -990,18 +1042,23 @@
         <v>0.9</v>
       </c>
       <c r="D20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="n">
         <v>0.5</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="10" t="n">
-        <v>0.9666666666666667</v>
       </c>
       <c r="G20" s="10" t="n">
         <v>0.9666666666666667</v>
       </c>
-      <c r="H20" s="3" t="inlineStr"/>
+      <c r="H20" s="10" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="I20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
@@ -1014,28 +1071,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C21" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="D21" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="n">
         <v>0.45</v>
       </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F21" s="14" t="n">
+      <c r="G21" s="13" t="n">
         <v>0.3</v>
       </c>
-      <c r="G21" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H21" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>CLS: testset_bycode 20장 · DET: 야장 20장</t>
         </is>
@@ -1052,28 +1110,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C22" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F22" s="14" t="n">
+      <c r="G22" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H22" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>CLS: testset_bycode 20장 · DET: 야장 20장</t>
         </is>
@@ -1092,18 +1151,23 @@
         <v>0.9</v>
       </c>
       <c r="D23" s="10" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="n">
         <v>0</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>0.9666666666666667</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>0.8666666666666667</v>
       </c>
       <c r="G23" s="10" t="n">
         <v>0.8666666666666667</v>
       </c>
-      <c r="H23" s="3" t="inlineStr"/>
+      <c r="H23" s="10" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="I23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
@@ -1118,18 +1182,23 @@
         <v>0.9</v>
       </c>
       <c r="D24" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="E24" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="10" t="n">
-        <v>1</v>
-      </c>
       <c r="G24" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H24" s="3" t="inlineStr"/>
+      <c r="H24" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
@@ -1142,7 +1211,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C25" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1152,7 +1221,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E25" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1162,12 +1231,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G25" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="G25" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>양쪽 데이터 없음</t>
         </is>
@@ -1184,28 +1258,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C26" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="D26" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="n">
         <v>0.95</v>
       </c>
-      <c r="E26" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="n">
+      <c r="G26" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="G26" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H26" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>CLS: testset_bycode 20장 · DET: 야장 10장 · DET 표본 10장</t>
         </is>
@@ -1222,30 +1297,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D27" s="13" t="n">
+      <c r="C27" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="n">
         <v>0.93</v>
       </c>
-      <c r="E27" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F27" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G27" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="G27" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H27" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>CLS: testset_bycode 15장 · YOLO 미학습</t>
         </is>
@@ -1264,18 +1342,23 @@
         <v>0.7333333333333333</v>
       </c>
       <c r="D28" s="10" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="n">
         <v>0.1</v>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>0.9666666666666667</v>
-      </c>
-      <c r="F28" s="10" t="n">
-        <v>0.9666666666666667</v>
       </c>
       <c r="G28" s="10" t="n">
         <v>0.9666666666666667</v>
       </c>
-      <c r="H28" s="3" t="inlineStr"/>
+      <c r="H28" s="10" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="I28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
@@ -1290,20 +1373,25 @@
         <v>1</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" s="10" t="n">
         <v>0.5333333333333333</v>
       </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F29" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="G29" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>YOLO에 클래스 없음 → DET 0%는 구조적</t>
+      <c r="H29" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>YOLO에 클래스 없음 → DET 이름 0%는 구조적</t>
         </is>
       </c>
     </row>
@@ -1318,28 +1406,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C30" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C30" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="n">
         <v>0.75</v>
       </c>
-      <c r="E30" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F30" s="14" t="n">
+      <c r="G30" s="13" t="n">
         <v>0.8</v>
       </c>
-      <c r="G30" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="H30" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
         <is>
           <t>CLS: testset_bycode 20장 · DET: 야장 20장</t>
         </is>
@@ -1356,28 +1445,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C31" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C31" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="n">
         <v>0.65</v>
       </c>
-      <c r="E31" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F31" s="14" t="n">
+      <c r="G31" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="G31" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="H31" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t>CLS: testset_bycode 20장 · DET: 야장 19장</t>
         </is>
@@ -1394,30 +1484,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D32" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F32" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G32" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="C32" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E32" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
         <is>
           <t>CLS: testset_bycode 20장 · YOLO 미학습</t>
         </is>
@@ -1434,7 +1527,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C33" s="12" t="inlineStr">
+      <c r="C33" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1444,7 +1537,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="E33" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1454,12 +1547,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G33" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="G33" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H33" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
         <is>
           <t>양쪽 데이터 없음</t>
         </is>
@@ -1476,30 +1574,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C34" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D34" s="13" t="n">
+      <c r="C34" s="12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E34" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E34" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F34" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G34" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="G34" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H34" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
         <is>
           <t>CLS: testset_bycode 20장 · 기타(결함 종류 아님)</t>
         </is>
@@ -1525,168 +1626,216 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CLS 이름정확도</t>
+          <t>DET 탐지율</t>
         </is>
       </c>
       <c r="B38" s="17" t="n">
-        <v>0.4083333333333333</v>
+        <v>0.8833333333333333</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DET 탐지율</t>
-        </is>
-      </c>
-      <c r="B39" s="17" t="n">
-        <v>0.8833333333333333</v>
+          <t>탐지 합집합(둘 중 하나라도 탐지)</t>
+        </is>
+      </c>
+      <c r="B39" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DET 이름정확도</t>
-        </is>
-      </c>
-      <c r="B40" s="17" t="n">
-        <v>0.6166666666666667</v>
+          <t>탐지 겹침(둘 다 탐지)</t>
+        </is>
+      </c>
+      <c r="B40" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>합집합(둘 중 하나라도 맞힘)</t>
+          <t>CLS 이름정확도</t>
         </is>
       </c>
       <c r="B41" s="17" t="n">
-        <v>0.9027777777777778</v>
+        <v>0.4083333333333333</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>겹침(둘 다 맞힘)</t>
+          <t>DET 이름정확도</t>
         </is>
       </c>
       <c r="B42" s="17" t="n">
-        <v>0.1222222222222222</v>
+        <v>0.6166666666666667</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CLS만 맞힘</t>
+          <t>이름 합집합(둘 중 하나라도 맞힘)</t>
         </is>
       </c>
       <c r="B43" s="17" t="n">
-        <v>0.2861111111111111</v>
+        <v>0.9027777777777778</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DET만 맞힘</t>
+          <t>이름 겹침(둘 다 맞힘)</t>
         </is>
       </c>
       <c r="B44" s="17" t="n">
+        <v>0.1222222222222222</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>이름 CLS만 맞힘</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="n">
+        <v>0.2861111111111111</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>이름 DET만 맞힘</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="n">
         <v>0.4944444444444445</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="16" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>[둘 다 아는 8종만] — 같은 종류 맞대결</t>
         </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>CLS 탐지율</t>
-        </is>
-      </c>
-      <c r="B47" s="17" t="n">
-        <v>0.8583333333333333</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>CLS 이름정확도</t>
-        </is>
-      </c>
-      <c r="B48" s="17" t="n">
-        <v>0.1833333333333333</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DET 탐지율</t>
+          <t>CLS 탐지율</t>
         </is>
       </c>
       <c r="B49" s="17" t="n">
-        <v>0.9833333333333333</v>
+        <v>0.8583333333333333</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DET 이름정확도</t>
+          <t>DET 탐지율</t>
         </is>
       </c>
       <c r="B50" s="17" t="n">
-        <v>0.925</v>
+        <v>0.9833333333333333</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>합집합(둘 중 하나라도 맞힘)</t>
-        </is>
-      </c>
-      <c r="B51" s="17" t="n">
-        <v>0.925</v>
+          <t>탐지 합집합(둘 중 하나라도 탐지)</t>
+        </is>
+      </c>
+      <c r="B51" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>겹침(둘 다 맞힘)</t>
-        </is>
-      </c>
-      <c r="B52" s="17" t="n">
-        <v>0.1833333333333333</v>
+          <t>탐지 겹침(둘 다 탐지)</t>
+        </is>
+      </c>
+      <c r="B52" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CLS만 맞힘</t>
+          <t>CLS 이름정확도</t>
         </is>
       </c>
       <c r="B53" s="17" t="n">
-        <v>0</v>
+        <v>0.1833333333333333</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DET만 맞힘</t>
+          <t>DET 이름정확도</t>
         </is>
       </c>
       <c r="B54" s="17" t="n">
+        <v>0.925</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>이름 합집합(둘 중 하나라도 맞힘)</t>
+        </is>
+      </c>
+      <c r="B55" s="17" t="n">
+        <v>0.925</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>이름 겹침(둘 다 맞힘)</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="n">
+        <v>0.1833333333333333</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>이름 CLS만 맞힘</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>이름 DET만 맞힘</t>
+        </is>
+      </c>
+      <c r="B58" s="17" t="n">
         <v>0.7416666666666667</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="B5:I5"/>
+    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="B4:I4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
